--- a/SIMULATION_DE_TRANSFERTS.xlsx
+++ b/SIMULATION_DE_TRANSFERTS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://villagereachorg-my.sharepoint.com/personal/kevin_guehou_ic_villagereach_org/Documents/Bureau/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_313D20FC6EE38D1FFD2D4C76AD2E3855797CF119" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8359895-0FA2-4244-B783-509B122382E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6457964-D85A-46EF-AA20-B85252BB8BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1316,7 +1316,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1682,9 +1682,6 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3120044</v>
-      </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
